--- a/hierarchy_color.xlsx
+++ b/hierarchy_color.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\CNS_tumor_proj\open_source\Paion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jindarui/Desktop/Hetairos_project/data_code/CNS_tumor_proj/open_source/Paion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B17493-ACFA-4D46-844A-5E8D8E3D149A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D254CA5C-8666-6E41-9CA3-6553A230655F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24583" yWindow="-12326" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="436">
   <si>
     <t>Molecular superfamily</t>
   </si>
@@ -1328,9 +1328,6 @@
     <t>control tissue, blood</t>
   </si>
   <si>
-    <t>cribriform neuroepithelial tumour</t>
-  </si>
-  <si>
     <t>desmoplastic myxoid tumour, SMARCB1-altered</t>
   </si>
   <si>
@@ -1338,17 +1335,26 @@
   </si>
   <si>
     <t>pineal/retinal RB1-related tumour</t>
+  </si>
+  <si>
+    <t>CNET</t>
+  </si>
+  <si>
+    <t>#4EA7D4</t>
+  </si>
+  <si>
+    <t>Cribriform neuroepithelial tumour</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1361,7 +1367,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1409,7 +1415,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1710,20 +1716,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L109"/>
-  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="45.23046875" customWidth="1"/>
-    <col min="3" max="4" width="17.61328125" customWidth="1"/>
-    <col min="5" max="5" width="20.69140625" customWidth="1"/>
-    <col min="6" max="6" width="20.84375" customWidth="1"/>
-    <col min="7" max="9" width="23.07421875" customWidth="1"/>
+    <col min="2" max="2" width="45.1640625" customWidth="1"/>
+    <col min="3" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="9" width="23" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1761,7 +1767,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1799,7 +1805,7 @@
         <v>2377</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1837,7 +1843,7 @@
         <v>2377</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1875,7 +1881,7 @@
         <v>2377</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1913,7 +1919,7 @@
         <v>2377</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1951,7 +1957,7 @@
         <v>2377</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1989,7 +1995,7 @@
         <v>2377</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2027,7 +2033,7 @@
         <v>2377</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>252</v>
       </c>
@@ -2065,7 +2071,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>252</v>
       </c>
@@ -2103,7 +2109,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>252</v>
       </c>
@@ -2141,7 +2147,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>252</v>
       </c>
@@ -2179,7 +2185,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>252</v>
       </c>
@@ -2217,7 +2223,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
         <v>252</v>
       </c>
@@ -2255,7 +2261,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>252</v>
       </c>
@@ -2293,7 +2299,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>252</v>
       </c>
@@ -2331,7 +2337,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
         <v>252</v>
       </c>
@@ -2369,7 +2375,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>252</v>
       </c>
@@ -2407,7 +2413,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>234</v>
       </c>
@@ -2445,7 +2451,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>234</v>
       </c>
@@ -2483,7 +2489,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>234</v>
       </c>
@@ -2521,7 +2527,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>234</v>
       </c>
@@ -2559,7 +2565,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -2597,7 +2603,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -2635,7 +2641,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -2673,7 +2679,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -2711,7 +2717,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -2749,7 +2755,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -2787,7 +2793,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -2825,7 +2831,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -2863,7 +2869,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -2901,7 +2907,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -2939,7 +2945,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -2977,7 +2983,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -3015,7 +3021,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
         <v>122</v>
       </c>
@@ -3053,7 +3059,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12">
       <c r="A36" t="s">
         <v>122</v>
       </c>
@@ -3091,7 +3097,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12">
       <c r="A37" t="s">
         <v>122</v>
       </c>
@@ -3129,7 +3135,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12">
       <c r="A38" t="s">
         <v>122</v>
       </c>
@@ -3167,7 +3173,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
         <v>203</v>
       </c>
@@ -3205,7 +3211,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12">
       <c r="A40" t="s">
         <v>203</v>
       </c>
@@ -3243,7 +3249,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12">
       <c r="A41" t="s">
         <v>203</v>
       </c>
@@ -3281,7 +3287,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12">
       <c r="A42" t="s">
         <v>203</v>
       </c>
@@ -3319,7 +3325,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
         <v>203</v>
       </c>
@@ -3357,7 +3363,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12">
       <c r="A44" t="s">
         <v>1</v>
       </c>
@@ -3395,7 +3401,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12">
       <c r="A45" t="s">
         <v>1</v>
       </c>
@@ -3433,7 +3439,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12">
       <c r="A46" t="s">
         <v>1</v>
       </c>
@@ -3471,7 +3477,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12">
       <c r="A47" t="s">
         <v>1</v>
       </c>
@@ -3509,7 +3515,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12">
       <c r="A48" t="s">
         <v>34</v>
       </c>
@@ -3547,7 +3553,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
         <v>34</v>
       </c>
@@ -3585,7 +3591,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12">
       <c r="A50" t="s">
         <v>34</v>
       </c>
@@ -3623,7 +3629,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12">
       <c r="A51" t="s">
         <v>34</v>
       </c>
@@ -3661,7 +3667,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12">
       <c r="A52" t="s">
         <v>34</v>
       </c>
@@ -3699,7 +3705,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12">
       <c r="A53" t="s">
         <v>34</v>
       </c>
@@ -3737,7 +3743,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12">
       <c r="A54" t="s">
         <v>34</v>
       </c>
@@ -3775,7 +3781,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12">
       <c r="A55" t="s">
         <v>40</v>
       </c>
@@ -3813,7 +3819,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12">
       <c r="A56" t="s">
         <v>40</v>
       </c>
@@ -3851,7 +3857,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12">
       <c r="A57" t="s">
         <v>40</v>
       </c>
@@ -3889,7 +3895,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12">
       <c r="A58" t="s">
         <v>40</v>
       </c>
@@ -3927,7 +3933,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12">
       <c r="A59" t="s">
         <v>40</v>
       </c>
@@ -3965,7 +3971,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -4003,7 +4009,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -4041,7 +4047,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12">
       <c r="A62" t="s">
         <v>59</v>
       </c>
@@ -4079,7 +4085,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12">
       <c r="A63" t="s">
         <v>59</v>
       </c>
@@ -4117,7 +4123,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12">
       <c r="A64" t="s">
         <v>59</v>
       </c>
@@ -4155,7 +4161,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12">
       <c r="A65" t="s">
         <v>59</v>
       </c>
@@ -4193,7 +4199,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12">
       <c r="A66" t="s">
         <v>99</v>
       </c>
@@ -4231,7 +4237,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12">
       <c r="A67" t="s">
         <v>99</v>
       </c>
@@ -4269,7 +4275,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12">
       <c r="A68" t="s">
         <v>168</v>
       </c>
@@ -4307,7 +4313,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12">
       <c r="A69" t="s">
         <v>168</v>
       </c>
@@ -4345,7 +4351,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12">
       <c r="A70" t="s">
         <v>282</v>
       </c>
@@ -4383,7 +4389,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12">
       <c r="A71" t="s">
         <v>282</v>
       </c>
@@ -4421,7 +4427,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12">
       <c r="A72" t="s">
         <v>282</v>
       </c>
@@ -4459,7 +4465,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12">
       <c r="A73" t="s">
         <v>282</v>
       </c>
@@ -4497,7 +4503,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12">
       <c r="A74" t="s">
         <v>282</v>
       </c>
@@ -4535,7 +4541,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12">
       <c r="A75" t="s">
         <v>282</v>
       </c>
@@ -4573,7 +4579,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12">
       <c r="A76" t="s">
         <v>188</v>
       </c>
@@ -4611,7 +4617,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12">
       <c r="A77" t="s">
         <v>188</v>
       </c>
@@ -4649,7 +4655,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12">
       <c r="A78" t="s">
         <v>188</v>
       </c>
@@ -4687,7 +4693,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12">
       <c r="A79" t="s">
         <v>154</v>
       </c>
@@ -4725,7 +4731,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12">
       <c r="A80" t="s">
         <v>154</v>
       </c>
@@ -4763,7 +4769,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12">
       <c r="A81" t="s">
         <v>154</v>
       </c>
@@ -4801,7 +4807,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12">
       <c r="A82" t="s">
         <v>259</v>
       </c>
@@ -4839,7 +4845,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12">
       <c r="A83" t="s">
         <v>259</v>
       </c>
@@ -4877,7 +4883,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12">
       <c r="A84" t="s">
         <v>259</v>
       </c>
@@ -4915,7 +4921,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12">
       <c r="A85" t="s">
         <v>66</v>
       </c>
@@ -4953,7 +4959,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12">
       <c r="A86" t="s">
         <v>66</v>
       </c>
@@ -4991,7 +4997,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12">
       <c r="A87" t="s">
         <v>366</v>
       </c>
@@ -5029,7 +5035,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12">
       <c r="A88" t="s">
         <v>52</v>
       </c>
@@ -5067,7 +5073,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12">
       <c r="A89" t="s">
         <v>52</v>
       </c>
@@ -5105,7 +5111,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12">
       <c r="A90" t="s">
         <v>180</v>
       </c>
@@ -5143,7 +5149,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12">
       <c r="A91" t="s">
         <v>288</v>
       </c>
@@ -5181,7 +5187,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12">
       <c r="A92" t="s">
         <v>26</v>
       </c>
@@ -5219,7 +5225,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12">
       <c r="A93" t="s">
         <v>229</v>
       </c>
@@ -5257,7 +5263,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12">
       <c r="A94" t="s">
         <v>271</v>
       </c>
@@ -5295,7 +5301,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12">
       <c r="A95" t="s">
         <v>47</v>
       </c>
@@ -5333,7 +5339,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12">
       <c r="A96" t="s">
         <v>114</v>
       </c>
@@ -5371,7 +5377,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12">
       <c r="A97" t="s">
         <v>224</v>
       </c>
@@ -5409,7 +5415,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12">
       <c r="A98" t="s">
         <v>121</v>
       </c>
@@ -5447,7 +5453,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12">
       <c r="A99" t="s">
         <v>377</v>
       </c>
@@ -5485,7 +5491,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12">
       <c r="A100" t="s">
         <v>278</v>
       </c>
@@ -5523,7 +5529,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12">
       <c r="A101" t="s">
         <v>194</v>
       </c>
@@ -5561,7 +5567,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12">
       <c r="A102" t="s">
         <v>274</v>
       </c>
@@ -5599,7 +5605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12">
       <c r="A103" t="s">
         <v>184</v>
       </c>
@@ -5637,7 +5643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12">
       <c r="A104" t="s">
         <v>99</v>
       </c>
@@ -5651,12 +5657,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12">
       <c r="A105" t="s">
         <v>34</v>
       </c>
       <c r="B105" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C105">
         <v>102</v>
@@ -5664,13 +5670,19 @@
       <c r="D105">
         <v>7</v>
       </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="F105" t="s">
+        <v>433</v>
+      </c>
+      <c r="I105" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
       <c r="A106" t="s">
         <v>114</v>
       </c>
       <c r="B106" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C106">
         <v>103</v>
@@ -5679,12 +5691,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12">
       <c r="A107" t="s">
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C107">
         <v>104</v>
@@ -5693,7 +5705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12">
       <c r="A108" t="s">
         <v>121</v>
       </c>
@@ -5707,12 +5719,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12">
       <c r="A109" t="s">
         <v>282</v>
       </c>
       <c r="B109" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C109">
         <v>107</v>
